--- a/ig/DM-JANVIER-2025/ValueSet-1.2.250.1.213.1.1.5.176.xlsx
+++ b/ig/DM-JANVIER-2025/ValueSet-1.2.250.1.213.1.1.5.176.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="42">
   <si>
     <t>Property</t>
   </si>
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20100101000000</t>
+    <t>20241230000000</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2010-01-01T00:00:00+01:00</t>
+    <t>2024-12-30T00:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -90,40 +90,46 @@
     <t>Concept</t>
   </si>
   <si>
-    <t>MED-382</t>
-  </si>
-  <si>
-    <t>Absence de symptômes</t>
-  </si>
-  <si>
-    <t>MED-383</t>
-  </si>
-  <si>
-    <t>Symptômes mineurs sans retentissement sur la vie quotidienne</t>
-  </si>
-  <si>
-    <t>MED-384</t>
-  </si>
-  <si>
-    <t>Symptôme ou handicap mineur qui conduit à certaines restrictions dans le mode de vie, mais qui n’interfère pas avec la capacité du patient à se prendre en charge</t>
-  </si>
-  <si>
-    <t>MED-385</t>
-  </si>
-  <si>
-    <t>Handicap modéré qui restreint significativement le mode de vie et/ou empêche une existence totalement indépendante</t>
-  </si>
-  <si>
-    <t>MED-386</t>
-  </si>
-  <si>
-    <t>Handicap modérément sévère qui empêche clairement une existence indépendante bien que nécessitant pas une attention constante</t>
-  </si>
-  <si>
-    <t>MED-387</t>
-  </si>
-  <si>
-    <t>Handicap sévère entraînant une dépendance totale et nécessitant une attention jour et nuit</t>
+    <t>LA6111-4</t>
+  </si>
+  <si>
+    <t>Aucun symptome</t>
+  </si>
+  <si>
+    <t>LA6112-2</t>
+  </si>
+  <si>
+    <t>Pas d’incapacité en dehors des symptomes : activités et autonomie conservées</t>
+  </si>
+  <si>
+    <t>LA6113-0</t>
+  </si>
+  <si>
+    <t>Handicap faible : incapable d’assurer les activités habituelles mais autonomie</t>
+  </si>
+  <si>
+    <t>LA6114-8</t>
+  </si>
+  <si>
+    <t>Handicap modéré : besoin d’aide mais marche possible sans assistance</t>
+  </si>
+  <si>
+    <t>LA6115-5</t>
+  </si>
+  <si>
+    <t>Handicap modérément sévère : marche et gestes quotidiens impossibles sans aide</t>
+  </si>
+  <si>
+    <t>LA10137-0</t>
+  </si>
+  <si>
+    <t>Handicap majeur : alitement permanent, incontinence et soins de nursing permanent</t>
+  </si>
+  <si>
+    <t>LA10138-8</t>
+  </si>
+  <si>
+    <t>Décédé</t>
   </si>
   <si>
     <t/>
@@ -132,7 +138,7 @@
     <t>System URI</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/CodeSystem/1.2.250.1.213.1.1.4.322</t>
+    <t>http://loinc.org</t>
   </si>
 </sst>
 </file>
@@ -388,7 +394,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -456,15 +462,23 @@
         <v>37</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B9" t="s" s="2">
         <v>39</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B10" t="s" s="2">
+        <v>41</v>
       </c>
     </row>
   </sheetData>
